--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2022_coquimbo.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2022_coquimbo.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:38</t>
+    <t xml:space="preserve">2026-09-24 01:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -993,13 +993,13 @@
         <v>-0.81</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>-0.75</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>-0.06</v>
@@ -1016,13 +1016,13 @@
         <v>-0.04</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>-0.23</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>0.19</v>
@@ -1039,13 +1039,13 @@
         <v>-0.7</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>-0.64</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>-0.06</v>
@@ -1059,19 +1059,19 @@
         <v>29</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>-0.52</v>
+        <v>-0.51</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>-0.4</v>
+        <v>-0.41</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="24">
@@ -1105,19 +1105,19 @@
         <v>35</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>-0.47</v>
+        <v>-0.44</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>15</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>-0.38</v>
+        <v>-0.23</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>329</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>-0.09</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="26">
@@ -1128,19 +1128,19 @@
         <v>35</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>-0.62</v>
+        <v>-0.63</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>15</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0.21</v>
+        <v>0.15</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>329</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>-0.83</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="27">
@@ -1151,19 +1151,19 @@
         <v>35</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>15</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>-0.21</v>
+        <v>-0.13</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>329</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="28">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2022_coquimbo.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2022_coquimbo.xlsx
@@ -126,7 +126,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:28</t>
+    <t xml:space="preserve">2026-10-01 23:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2022_coquimbo.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2022_coquimbo.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:12</t>
+    <t xml:space="preserve">2026-10-05 19:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
